--- a/data/trans_orig/IP31B_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_R_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27618</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23012</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31071</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>74,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28196</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32950</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55389</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6066</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14125</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15840</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11086</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21163</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60195</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51094</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70024</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>67798</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57835</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72427</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61506</t>
+          <t>52553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83563</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>140225</t>
+          <t>121376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125228</t>
+          <t>108499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154548</t>
+          <t>135339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95341</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85512</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>104442</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>91110</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81172</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101073</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>57,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>106851</t>
+          <t>83997</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95715</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>92624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>197961</t>
+          <t>179338</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183638</t>
+          <t>165375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212958</t>
+          <t>192215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60286</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48710</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70978</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41400</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32481</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51711</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78415</t>
+          <t>52848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>106352</t>
+          <t>102715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91799</t>
+          <t>88221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123192</t>
+          <t>118894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137808</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127116</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>131672</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121361</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>76,08%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>145435</t>
+          <t>132244</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131972</t>
+          <t>121824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157229</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>277107</t>
+          <t>270052</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260267</t>
+          <t>253873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291660</t>
+          <t>284546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>77758</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63199</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97262</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>82334</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56263</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>141567</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87749</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70229</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109995</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>133041</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138268</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239208</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>214463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>194959</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>229022</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>190849</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>131616</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>216920</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217250</t>
+          <t>198866</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195004</t>
+          <t>186423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234770</t>
+          <t>210349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>408099</t>
+          <t>413329</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338974</t>
+          <t>391217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>439914</t>
+          <t>433426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>225858</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>204522</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>250878</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>219727</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192703</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>282508</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>165303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>203868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>440688</t>
+          <t>380431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>541957</t>
+          <t>441822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>457130</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>432110</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>478466</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>429472</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>366691</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>456496</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>480404</t>
+          <t>430773</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451139</t>
+          <t>410708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505945</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>909876</t>
+          <t>887903</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846795</t>
+          <t>855743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>948064</t>
+          <t>917134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
